--- a/docs/assets/3rdparty/source/VocExcel-ice-cream-flavor-concepts.xlsx
+++ b/docs/assets/3rdparty/source/VocExcel-ice-cream-flavor-concepts.xlsx
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="405">
   <si>
     <t>Version:</t>
   </si>
@@ -1705,7 +1705,7 @@
     <t>FRUIT FLAVORS</t>
   </si>
   <si>
-    <t>icf:45b0a9d3-d3c9-4c19-b4ef-0511a8827101</t>
+    <t>icf:2</t>
   </si>
   <si>
     <t>Banana</t>
@@ -1714,7 +1714,7 @@
     <t>Banana ice cream flavor</t>
   </si>
   <si>
-    <t>icf:abf359ff-5c42-42e1-91a5-21973879f6f0</t>
+    <t>icf:3</t>
   </si>
   <si>
     <t>Black raspberry</t>
@@ -1723,7 +1723,7 @@
     <t>Black raspberry ice cream flavor</t>
   </si>
   <si>
-    <t>icf:0f748e6f-ae0b-49a9-bac9-98db1de6fd04</t>
+    <t>icf:4</t>
   </si>
   <si>
     <t xml:space="preserve">Cherry </t>
@@ -1735,7 +1735,7 @@
     <t>Amaretto cherry, black cherry</t>
   </si>
   <si>
-    <t>icf:bf94fff7-9ef5-4af6-91dc-bf332e1bbd72</t>
+    <t>icf:5</t>
   </si>
   <si>
     <t>Cinnamon apple</t>
@@ -1744,7 +1744,7 @@
     <t>Cinnamon apple ice cream flavor</t>
   </si>
   <si>
-    <t>icf:556b0f61-f107-4519-8bbe-cf3c29d840bb</t>
+    <t>icf:6</t>
   </si>
   <si>
     <t>Grape</t>
@@ -1753,7 +1753,7 @@
     <t>Grape ice cream flavor</t>
   </si>
   <si>
-    <t>icf:79aaa965-5e88-4a01-8b5a-87438ff46cf6</t>
+    <t>icf:7</t>
   </si>
   <si>
     <t xml:space="preserve">Lúcuma </t>
@@ -1762,13 +1762,13 @@
     <t xml:space="preserve"> A popular Peruvian ice cream flavor with an orange color and a sweet nutty taste</t>
   </si>
   <si>
-    <t>icf:4343af06-9db2-43d4-920a-61d349ef42f5</t>
+    <t>icf:8</t>
   </si>
   <si>
     <t>Mamey</t>
   </si>
   <si>
-    <t>icf:f476202a-b952-4b55-8877-33570ee26cf5</t>
+    <t>icf:9</t>
   </si>
   <si>
     <t>Mango</t>
@@ -1777,7 +1777,7 @@
     <t>Mango ice cream flavor</t>
   </si>
   <si>
-    <t>icf:cd2071b4-cb2e-4c12-ad82-fa7b2c844899</t>
+    <t>icf:10</t>
   </si>
   <si>
     <t xml:space="preserve">Moon mist </t>
@@ -1786,7 +1786,7 @@
     <t>A blend of grape, banana, and blue raspberry (or sometimes bubblegum) flavors, popular in Atlantic Canada. The flavors are generally blended together to give a mist-like texture.</t>
   </si>
   <si>
-    <t>icf:61ed4c66-f7d8-40c9-8866-cc4bdee3ea44</t>
+    <t>icf:11</t>
   </si>
   <si>
     <t>Passion fruit</t>
@@ -1795,7 +1795,7 @@
     <t>Passion fruit ice cream flavor</t>
   </si>
   <si>
-    <t>icf:9e8afe4c-f6db-40e3-a625-7dbeadc1a3d5</t>
+    <t>icf:12</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -1804,7 +1804,7 @@
     <t>Pumpkin ice cream flavor</t>
   </si>
   <si>
-    <t>icf:a5120bb8-2a39-4b7e-95e4-c05646ab53e2</t>
+    <t>icf:13</t>
   </si>
   <si>
     <t xml:space="preserve">Raspberry ripple </t>
@@ -1813,7 +1813,7 @@
     <t xml:space="preserve"> Consists of raspberry syrup injected into vanilla ice cream.</t>
   </si>
   <si>
-    <t>icf:7b276e8c-ac83-4eb0-8b8d-e26f0f00d190</t>
+    <t>icf:14</t>
   </si>
   <si>
     <t>Rum raisin</t>
@@ -1822,7 +1822,7 @@
     <t>Rum raisin ice cream flavor</t>
   </si>
   <si>
-    <t>icf:ccb7b867-4f44-4eea-bd09-99f964664733</t>
+    <t>icf:15</t>
   </si>
   <si>
     <t>Strawberry</t>
@@ -1831,7 +1831,7 @@
     <t>Strawberry ice cream flavor</t>
   </si>
   <si>
-    <t>icf:b8af11ac-39c5-4547-8ff0-1cb77e50f9d5</t>
+    <t>icf:16</t>
   </si>
   <si>
     <t>Strawberry cheesecake</t>
@@ -1840,7 +1840,7 @@
     <t>Strawberry cheesecake ice cream flavor</t>
   </si>
   <si>
-    <t>icf:bd9289fa-9715-4a2e-89bd-bc4f705dc167</t>
+    <t>icf:17</t>
   </si>
   <si>
     <t>Superman</t>
@@ -1849,7 +1849,7 @@
     <t xml:space="preserve">Superman ice cream is a three-flavor ice cream that usually appears in red, blue, and yellow. </t>
   </si>
   <si>
-    <t>icf:0e9b17d8-339c-4a55-8157-03b15be56f76</t>
+    <t>icf:18</t>
   </si>
   <si>
     <t>Teaberry</t>
@@ -1858,7 +1858,7 @@
     <t>Teaberry ice cream is an ice cream flavor made with the eastern teaberry fruit. </t>
   </si>
   <si>
-    <t>icf:d35b1641-f112-4ab5-83fe-95e98229f4e7</t>
+    <t>icf:19</t>
   </si>
   <si>
     <t xml:space="preserve">Tiger tail </t>
@@ -1867,7 +1867,7 @@
     <t>A flavor popular in Canada, consisting of orange-flavored ice cream with swirls of black licorice</t>
   </si>
   <si>
-    <t>icf:a1a144fd-3f41-4961-9bb1-47ac783232b5</t>
+    <t>icf:20</t>
   </si>
   <si>
     <t>Tutti frutti</t>
@@ -1876,7 +1876,7 @@
     <t>Tutti frutti ice cream flavor</t>
   </si>
   <si>
-    <t>icf:9de1e781-4733-4cbe-8cb2-143d7a4ed92f</t>
+    <t>icf:21</t>
   </si>
   <si>
     <t>Watermelon</t>
@@ -1885,7 +1885,7 @@
     <t>CHOCOLATE, NUTS AND OTHER SWEETS</t>
   </si>
   <si>
-    <t>icf:e702da60-1dbe-48ee-891f-e1de99ee07d5</t>
+    <t>icf:23</t>
   </si>
   <si>
     <t xml:space="preserve">Biscuit Tortoni </t>
@@ -1894,7 +1894,7 @@
     <t>An ice cream made with eggs and heavy cream, often containing chopped cherries or topped with minced almonds or crumbled macaroons</t>
   </si>
   <si>
-    <t>icf:2f524245-e21c-4c02-966d-f3b4022535ea</t>
+    <t>icf:24</t>
   </si>
   <si>
     <t xml:space="preserve">Blue moon </t>
@@ -1903,7 +1903,7 @@
     <t>An ice cream flavor with bright blue coloring, available in the Upper Midwest of the United States</t>
   </si>
   <si>
-    <t>icf:c4c2344c-4b1b-462a-b9f9-e1b03faeb0dd</t>
+    <t>icf:25</t>
   </si>
   <si>
     <t>Bubblegum</t>
@@ -1912,7 +1912,7 @@
     <t>Bubblegum ice cream flavor</t>
   </si>
   <si>
-    <t>icf:f4fe093d-96d6-4419-8079-1fdba8a479cc</t>
+    <t>icf:26</t>
   </si>
   <si>
     <t xml:space="preserve">Butter Brickle </t>
@@ -1921,7 +1921,7 @@
     <t>The registered trademark of a toffee ice cream flavoring and of a toffee-centered chocolate-covered candy bar similar to the Heath bar, introduced by the Blackstone Hotel in Omaha, Nebraska, in the 1920s. Alternately, it is often prepared and sold as butter vanilla-flavored ice cream with tiny flecks of butter toffee instead of chunks of Heath bar.</t>
   </si>
   <si>
-    <t>icf:66dcdd54-fffb-4d29-90bc-0be9a9d052b5</t>
+    <t>icf:27</t>
   </si>
   <si>
     <t>Butterscotch</t>
@@ -1930,7 +1930,7 @@
     <t>Butterscotch ice cream flavor</t>
   </si>
   <si>
-    <t>icf:a61185c1-786a-4a93-8964-0d53686baddd</t>
+    <t>icf:28</t>
   </si>
   <si>
     <t xml:space="preserve">Butter pecan </t>
@@ -1939,7 +1939,7 @@
     <t>A smooth vanilla ice cream with a slight buttery flavor, with pecans added.</t>
   </si>
   <si>
-    <t>icf:aa64a8c2-8dbb-428b-94f9-fc328870d3ec</t>
+    <t>icf:29</t>
   </si>
   <si>
     <t>Cake batter</t>
@@ -1948,7 +1948,7 @@
     <t>Cake batter ice cream flavor</t>
   </si>
   <si>
-    <t>icf:2307a8fb-e802-403a-b255-6ec1a57677aa</t>
+    <t>icf:30</t>
   </si>
   <si>
     <t>Caramel</t>
@@ -1957,7 +1957,7 @@
     <t>Caramel ice cream flavor</t>
   </si>
   <si>
-    <t>icf:e8555003-5203-47d4-af04-70798add66ad</t>
+    <t>icf:31</t>
   </si>
   <si>
     <t>Chocolate</t>
@@ -1966,7 +1966,7 @@
     <t>Chocolate ice cream is ice cream with natural or artificial chocolate flavoring.</t>
   </si>
   <si>
-    <t>icf:f7bbc944-ecdc-4517-8f71-6ac6653db5c4</t>
+    <t>icf:32</t>
   </si>
   <si>
     <t xml:space="preserve">Chocolate chip </t>
@@ -1975,7 +1975,7 @@
     <t>Vanilla base, with chunks of solid chocolate. Declining in popularity in the 2020s. Sometimes chocolate ice cream was used, which was usually called "Chocolate chocolate chip"</t>
   </si>
   <si>
-    <t>icf:678299ea-ae67-4736-b109-02f3b5c2e752</t>
+    <t>icf:33</t>
   </si>
   <si>
     <t>Chocolate chip cookie dough</t>
@@ -1984,7 +1984,7 @@
     <t>Chocolate chip cookie dough ice cream flavor</t>
   </si>
   <si>
-    <t>icf:cd7ecf43-79b3-4495-98a5-fea33b86a29c</t>
+    <t>icf:34</t>
   </si>
   <si>
     <t>Coffee</t>
@@ -1993,7 +1993,7 @@
     <t>Coffee ice cream is an ice cream flavor made with coffee or coffee flavoring.</t>
   </si>
   <si>
-    <t>icf:10cdc74f-c236-42cf-bb32-33f40c882189</t>
+    <t>icf:35</t>
   </si>
   <si>
     <t>Cookies and cream</t>
@@ -2002,7 +2002,7 @@
     <t>Cookies and cream ice cream flavor</t>
   </si>
   <si>
-    <t>icf:1619cc1c-c75b-45d1-bdaf-ced29978673f</t>
+    <t>icf:36</t>
   </si>
   <si>
     <t>Cotton candy</t>
@@ -2011,7 +2011,7 @@
     <t>Cotton candy ice cream flavor</t>
   </si>
   <si>
-    <t>icf:bbe41b1a-5eb1-4d35-af25-673b0c0c842d</t>
+    <t>icf:37</t>
   </si>
   <si>
     <t>Dulce de leche</t>
@@ -2020,7 +2020,7 @@
     <t>Dulce de leche ice cream flavor</t>
   </si>
   <si>
-    <t>icf:98656441-5fd4-42e8-bd11-cfce8fae4a86</t>
+    <t>icf:38</t>
   </si>
   <si>
     <t>Earl Grey tea</t>
@@ -2029,7 +2029,7 @@
     <t>Earl Grey tea ice cream flavor</t>
   </si>
   <si>
-    <t>icf:6148a62f-1ae4-4797-9f6a-359f17c2c60a</t>
+    <t>icf:39</t>
   </si>
   <si>
     <t>Eggnog</t>
@@ -2038,7 +2038,7 @@
     <t>Eggnog ice cream flavor</t>
   </si>
   <si>
-    <t>icf:f8892819-70b5-4efc-8e42-43d1024d943e</t>
+    <t>icf:40</t>
   </si>
   <si>
     <t>French vanilla</t>
@@ -2047,7 +2047,7 @@
     <t>French vanilla ice cream flavor</t>
   </si>
   <si>
-    <t>icf:d4ef5ab1-2fd4-4b70-b7a0-ad79605f5e4e</t>
+    <t>icf:41</t>
   </si>
   <si>
     <t xml:space="preserve">Goody Goody Gum Drops </t>
@@ -2056,7 +2056,7 @@
     <t>Goody Goody Gum Drops ice cream flavor, unique to New Zealand</t>
   </si>
   <si>
-    <t>icf:5c2bad30-3036-4394-abef-1daf0cb6351d</t>
+    <t>icf:42</t>
   </si>
   <si>
     <t>Green tea</t>
@@ -2065,7 +2065,7 @@
     <t>Green tea  ice cream flavor</t>
   </si>
   <si>
-    <t>icf:07ff3c57-c075-4a95-be6a-99955621dd5c</t>
+    <t>icf:43</t>
   </si>
   <si>
     <t>Halva</t>
@@ -2074,7 +2074,7 @@
     <t>Halva ice cream flavor</t>
   </si>
   <si>
-    <t>icf:3c71c026-00b2-435e-bb8b-66d006e7b133</t>
+    <t>icf:44</t>
   </si>
   <si>
     <t xml:space="preserve">Hokey pokey </t>
@@ -2083,7 +2083,7 @@
     <t>a flavor of ice cream in New Zealand, consisting of plain vanilla ice cream with small, solid lumps of honeycomb toffee</t>
   </si>
   <si>
-    <t>icf:ade1b5f0-58c6-46a8-8faa-6ed4224c72b7</t>
+    <t>icf:45</t>
   </si>
   <si>
     <t>Maple</t>
@@ -2092,7 +2092,7 @@
     <t>Maple ice cream flavor</t>
   </si>
   <si>
-    <t>icf:23798250-a926-42ba-95ce-c5576efa0bec</t>
+    <t>icf:46</t>
   </si>
   <si>
     <t xml:space="preserve">Mint chocolate chip </t>
@@ -2101,7 +2101,7 @@
     <t>Composed of mint ice cream with small chocolate chips. In some cases the liqueur crème de menthe is used to provide the mint flavor, but in most cases peppermint or spearmint flavoring is used.</t>
   </si>
   <si>
-    <t>icf:a886dea1-e597-40a2-84c2-f91f1750c724</t>
+    <t>icf:47</t>
   </si>
   <si>
     <t>Moose tracks</t>
@@ -2110,7 +2110,7 @@
     <t>Moose tracks ice cream flavor</t>
   </si>
   <si>
-    <t>icf:06f52b88-9ad0-4214-bf41-f5c23514d2cd</t>
+    <t>icf:48</t>
   </si>
   <si>
     <t xml:space="preserve">Neapolitan </t>
@@ -2119,7 +2119,7 @@
     <t xml:space="preserve"> Composed of vanilla, chocolate and strawberry ice cream together side by side</t>
   </si>
   <si>
-    <t>icf:28d8e6bb-6003-451e-b21e-292b4c5067f4</t>
+    <t>icf:49</t>
   </si>
   <si>
     <t>Pistachio</t>
@@ -2128,7 +2128,7 @@
     <t>Pistachio ice cream flavor</t>
   </si>
   <si>
-    <t>icf:48493fe1-dccb-45d0-9082-90ee9cb2e2f6</t>
+    <t>icf:50</t>
   </si>
   <si>
     <t>Peanut butter</t>
@@ -2137,7 +2137,7 @@
     <t>Peanut butter ice cream flavor</t>
   </si>
   <si>
-    <t>icf:cf5e8785-f0d9-4d8f-bcd8-c196b3751051</t>
+    <t>icf:51</t>
   </si>
   <si>
     <t xml:space="preserve">Rocky road </t>
@@ -2146,7 +2146,7 @@
     <t>Although there are variations from the original flavor, it is traditionally composed of chocolate ice cream, nuts, and whole or diced marshmallows, or sometimes replaced with marshmallow creme, a more fluid version</t>
   </si>
   <si>
-    <t>icf:a91c45b3-4168-4326-ba6f-6300858fde67</t>
+    <t>icf:52</t>
   </si>
   <si>
     <t>Rose</t>
@@ -2155,7 +2155,7 @@
     <t>Rose ice cream flavor</t>
   </si>
   <si>
-    <t>icf:a06e660a-7ca5-4213-88a9-5c2ea3574899</t>
+    <t>icf:53</t>
   </si>
   <si>
     <t xml:space="preserve">Spumoni </t>
@@ -2164,7 +2164,7 @@
     <t>A molded Italian ice cream made with layers of different colors and flavors, usually containing candied fruits and nuts.</t>
   </si>
   <si>
-    <t>icf:8f32f706-4827-4b52-8658-97af4cfa0398</t>
+    <t>icf:54</t>
   </si>
   <si>
     <t>Stracciatella</t>
@@ -2173,7 +2173,7 @@
     <t>Stracciatella ice cream flavor</t>
   </si>
   <si>
-    <t>icf:295b3fc1-a889-4960-bdbd-304392d1f0ec</t>
+    <t>icf:55</t>
   </si>
   <si>
     <t>Thai tea</t>
@@ -2182,7 +2182,7 @@
     <t>Thai tea ice cream flavor</t>
   </si>
   <si>
-    <t>icf:033da6cd-a916-467c-bbea-a6cd7b2fd9a3</t>
+    <t>icf:56</t>
   </si>
   <si>
     <t xml:space="preserve">Tramontana </t>
@@ -2191,7 +2191,7 @@
     <t>Composed of dark chocolate, white chocolate, dulce de leche and cookies.</t>
   </si>
   <si>
-    <t>icf:f8463b04-fa44-41b7-bb42-acc83a089cbb</t>
+    <t>icf:57</t>
   </si>
   <si>
     <t>Vanilla</t>
@@ -2203,7 +2203,7 @@
     <t>SAVORY FLAVORS</t>
   </si>
   <si>
-    <t>icf:cc6b3ba1-b7ef-4ea9-b60a-77c52c1bb74d</t>
+    <t>icf:59</t>
   </si>
   <si>
     <t xml:space="preserve">Bacon </t>
@@ -2212,7 +2212,7 @@
     <t>A modern invention, generally created by adding bacon to egg custard and freezing the mixture</t>
   </si>
   <si>
-    <t>icf:e54eea7d-074b-4d7b-8d73-d0df22b1f3e3</t>
+    <t>icf:60</t>
   </si>
   <si>
     <t>Beer</t>
@@ -2221,7 +2221,7 @@
     <t>Beer ice cream flavor</t>
   </si>
   <si>
-    <t>icf:2db0fe98-c26f-4cde-955e-53e0cbe5ee8e</t>
+    <t>icf:61</t>
   </si>
   <si>
     <t>Carrot</t>
@@ -2230,7 +2230,7 @@
     <t>Carrot ice cream flavor</t>
   </si>
   <si>
-    <t>icf:abb0e61b-5c54-4984-a13b-780563887653</t>
+    <t>icf:62</t>
   </si>
   <si>
     <t>Cheese</t>
@@ -2239,7 +2239,7 @@
     <t>Cheese ice cream flavor</t>
   </si>
   <si>
-    <t>icf:f550c468-b125-49ff-a3f2-1876954f7f73</t>
+    <t>icf:63</t>
   </si>
   <si>
     <t xml:space="preserve">Crab </t>
@@ -2248,7 +2248,7 @@
     <t>A Japanese creation,it is described as having a sweet taste; the island of Hokkaido, Japan, is known for manufacturing it</t>
   </si>
   <si>
-    <t>icf:1671e56f-52db-48af-a0a5-e45f8eb66053</t>
+    <t>icf:64</t>
   </si>
   <si>
     <t>Creole cream cheese</t>
@@ -2257,7 +2257,7 @@
     <t>Creole cream cheese ice cream flavor</t>
   </si>
   <si>
-    <t>icf:88947dcc-ef36-4bda-b26f-d91b9bbb92d9</t>
+    <t>icf:65</t>
   </si>
   <si>
     <t>Garlic</t>
@@ -2266,7 +2266,7 @@
     <t>Garlic ice cream flavor</t>
   </si>
   <si>
-    <t>icf:b868d0d7-e574-48b0-a6b2-433a01c7434a</t>
+    <t>icf:66</t>
   </si>
   <si>
     <t>Oyster</t>
@@ -2275,7 +2275,7 @@
     <t>Oyster ice cream flavor</t>
   </si>
   <si>
-    <t>icf:b023c80a-7d05-4324-8207-4e5bba5dec17</t>
+    <t>icf:67</t>
   </si>
   <si>
     <t>Korean Sweet corn</t>
@@ -2284,7 +2284,7 @@
     <t>Korean Sweet corn ice cream flavor</t>
   </si>
   <si>
-    <t>icf:96e04174-022b-4934-a431-3bb3f96f015f</t>
+    <t>icf:68</t>
   </si>
   <si>
     <t>Taro</t>
@@ -2293,7 +2293,7 @@
     <t>Taro ice cream flavor</t>
   </si>
   <si>
-    <t>icf:392def8f-2e32-4c23-ae4f-2f149787f3a6</t>
+    <t>icf:69</t>
   </si>
   <si>
     <t xml:space="preserve">Spundekas </t>
@@ -2302,7 +2302,7 @@
     <t>Ice cream flavor based on the German cream cheese of the same name</t>
   </si>
   <si>
-    <t>icf:8e63e629-3b8f-47d7-86d8-079bc74dc92c</t>
+    <t>icf:70</t>
   </si>
   <si>
     <t>Ube</t>
@@ -2312,6 +2312,15 @@
   </si>
   <si>
     <t>purple yam</t>
+  </si>
+  <si>
+    <t>icf:1</t>
+  </si>
+  <si>
+    <t>icf:22</t>
+  </si>
+  <si>
+    <t>icf:58</t>
   </si>
 </sst>
 </file>
@@ -7863,9 +7872,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B2936F-06B6-364A-893D-D48542B6FA7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns6="http://schemas.microsoft.com/office/excel/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{65B2936F-06B6-364A-893D-D48542B6FA7F}">
   <dimension ref="A1:L76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="18" ns3:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="49.1640625" style="21" customWidth="1"/>
     <col min="2" max="2" width="58.33203125" style="21" customWidth="1"/>
@@ -7880,7 +7889,7 @@
     <col min="13" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" ht="40" customHeight="1" ns3:dyDescent="0.15">
       <c r="A1" s="63" t="s">
         <v>13</v>
       </c>
@@ -7892,7 +7901,7 @@
       <c r="G1" s="63"/>
       <c r="H1" s="63"/>
     </row>
-    <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" ht="19" ns3:dyDescent="0.15">
       <c r="A2" s="32" t="s">
         <v>56</v>
       </c>
@@ -7930,7 +7939,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="271" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" ht="271" customHeight="1" ns3:dyDescent="0.15">
       <c r="A3" s="27" t="s">
         <v>183</v>
       </c>
@@ -7968,8 +7977,10 @@
         <v>163</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="59"/>
+    <row r="4" spans="1:12" ns3:dyDescent="0.2">
+      <c r="A4" s="59" t="s">
+        <v>402</v>
+      </c>
       <c r="B4" s="60" t="s">
         <v>198</v>
       </c>
@@ -7978,7 +7989,7 @@
       <c r="E4" s="20"/>
       <c r="G4" s="20"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ns3:dyDescent="0.2">
       <c r="A5" s="59" t="s">
         <v>199</v>
       </c>
@@ -7991,7 +8002,7 @@
       <c r="D5" s="59"/>
       <c r="G5" s="20"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ns3:dyDescent="0.2">
       <c r="A6" s="59" t="s">
         <v>202</v>
       </c>
@@ -8005,7 +8016,7 @@
       <c r="G6" s="20"/>
       <c r="K6" s="20"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ns3:dyDescent="0.2">
       <c r="A7" s="59" t="s">
         <v>205</v>
       </c>
@@ -8020,7 +8031,7 @@
       </c>
       <c r="G7" s="56"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" ns3:dyDescent="0.2">
       <c r="A8" s="59" t="s">
         <v>209</v>
       </c>
@@ -8033,7 +8044,7 @@
       <c r="D8" s="59"/>
       <c r="G8" s="56"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" ns3:dyDescent="0.2">
       <c r="A9" s="59" t="s">
         <v>212</v>
       </c>
@@ -8046,7 +8057,7 @@
       <c r="D9" s="59"/>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ns3:dyDescent="0.2">
       <c r="A10" s="59" t="s">
         <v>215</v>
       </c>
@@ -8059,7 +8070,7 @@
       <c r="D10" s="59"/>
       <c r="G10" s="56"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ns3:dyDescent="0.2">
       <c r="A11" s="59" t="s">
         <v>218</v>
       </c>
@@ -8072,7 +8083,7 @@
       <c r="D11" s="59"/>
       <c r="G11" s="56"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" ns3:dyDescent="0.2">
       <c r="A12" s="59" t="s">
         <v>220</v>
       </c>
@@ -8085,7 +8096,7 @@
       <c r="D12" s="59"/>
       <c r="G12" s="56"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" ns3:dyDescent="0.2">
       <c r="A13" s="59" t="s">
         <v>223</v>
       </c>
@@ -8098,7 +8109,7 @@
       <c r="D13" s="59"/>
       <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ns3:dyDescent="0.2">
       <c r="A14" s="59" t="s">
         <v>226</v>
       </c>
@@ -8111,7 +8122,7 @@
       <c r="D14" s="59"/>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" ns3:dyDescent="0.2">
       <c r="A15" s="59" t="s">
         <v>229</v>
       </c>
@@ -8124,7 +8135,7 @@
       <c r="D15" s="59"/>
       <c r="G15" s="56"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" ns3:dyDescent="0.2">
       <c r="A16" s="59" t="s">
         <v>232</v>
       </c>
@@ -8137,7 +8148,7 @@
       <c r="D16" s="59"/>
       <c r="G16" s="56"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ns3:dyDescent="0.2">
       <c r="A17" s="59" t="s">
         <v>235</v>
       </c>
@@ -8151,7 +8162,7 @@
       <c r="E17" s="44"/>
       <c r="G17" s="20"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ns3:dyDescent="0.2">
       <c r="A18" s="59" t="s">
         <v>238</v>
       </c>
@@ -8165,7 +8176,7 @@
       <c r="E18" s="44"/>
       <c r="G18" s="56"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ns3:dyDescent="0.2">
       <c r="A19" s="59" t="s">
         <v>241</v>
       </c>
@@ -8178,7 +8189,7 @@
       <c r="D19" s="59"/>
       <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ns3:dyDescent="0.2">
       <c r="A20" s="59" t="s">
         <v>244</v>
       </c>
@@ -8191,7 +8202,7 @@
       <c r="D20" s="59"/>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ns3:dyDescent="0.2">
       <c r="A21" s="59" t="s">
         <v>247</v>
       </c>
@@ -8204,7 +8215,7 @@
       <c r="D21" s="59"/>
       <c r="G21" s="20"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ns3:dyDescent="0.2">
       <c r="A22" s="59" t="s">
         <v>250</v>
       </c>
@@ -8217,7 +8228,7 @@
       <c r="D22" s="59"/>
       <c r="G22" s="20"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ns3:dyDescent="0.2">
       <c r="A23" s="59" t="s">
         <v>253</v>
       </c>
@@ -8230,7 +8241,7 @@
       <c r="D23" s="59"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ns3:dyDescent="0.2">
       <c r="A24" s="59" t="s">
         <v>256</v>
       </c>
@@ -8243,15 +8254,17 @@
       <c r="D24" s="59"/>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ns3:dyDescent="0.2">
       <c r="A25" s="59"/>
       <c r="B25" s="60"/>
       <c r="C25" s="60"/>
       <c r="D25" s="59"/>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="59"/>
+    <row r="26" spans="1:7" ns3:dyDescent="0.2">
+      <c r="A26" s="59" t="s">
+        <v>403</v>
+      </c>
       <c r="B26" s="60" t="s">
         <v>258</v>
       </c>
@@ -8259,7 +8272,7 @@
       <c r="D26" s="59"/>
       <c r="G26" s="20"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ns3:dyDescent="0.2">
       <c r="A27" s="59" t="s">
         <v>259</v>
       </c>
@@ -8272,7 +8285,7 @@
       <c r="D27" s="59"/>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ns3:dyDescent="0.2">
       <c r="A28" s="59" t="s">
         <v>262</v>
       </c>
@@ -8285,7 +8298,7 @@
       <c r="D28" s="59"/>
       <c r="G28" s="20"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ns3:dyDescent="0.2">
       <c r="A29" s="59" t="s">
         <v>265</v>
       </c>
@@ -8298,7 +8311,7 @@
       <c r="D29" s="59"/>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ns3:dyDescent="0.2">
       <c r="A30" s="59" t="s">
         <v>268</v>
       </c>
@@ -8311,7 +8324,7 @@
       <c r="D30" s="59"/>
       <c r="G30" s="20"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ns3:dyDescent="0.2">
       <c r="A31" s="59" t="s">
         <v>271</v>
       </c>
@@ -8324,7 +8337,7 @@
       <c r="D31" s="59"/>
       <c r="G31" s="20"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ns3:dyDescent="0.2">
       <c r="A32" s="59" t="s">
         <v>274</v>
       </c>
@@ -8337,7 +8350,7 @@
       <c r="D32" s="59"/>
       <c r="G32" s="20"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ns3:dyDescent="0.2">
       <c r="A33" s="59" t="s">
         <v>277</v>
       </c>
@@ -8350,7 +8363,7 @@
       <c r="D33" s="59"/>
       <c r="G33" s="20"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ns3:dyDescent="0.2">
       <c r="A34" s="59" t="s">
         <v>280</v>
       </c>
@@ -8363,7 +8376,7 @@
       <c r="D34" s="59"/>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ns3:dyDescent="0.2">
       <c r="A35" s="59" t="s">
         <v>283</v>
       </c>
@@ -8376,7 +8389,7 @@
       <c r="D35" s="59"/>
       <c r="G35" s="20"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ns3:dyDescent="0.2">
       <c r="A36" s="59" t="s">
         <v>286</v>
       </c>
@@ -8389,7 +8402,7 @@
       <c r="D36" s="59"/>
       <c r="G36" s="20"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ns3:dyDescent="0.2">
       <c r="A37" s="59" t="s">
         <v>289</v>
       </c>
@@ -8402,7 +8415,7 @@
       <c r="D37" s="59"/>
       <c r="G37" s="20"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ns3:dyDescent="0.2">
       <c r="A38" s="59" t="s">
         <v>292</v>
       </c>
@@ -8415,7 +8428,7 @@
       <c r="D38" s="59"/>
       <c r="G38" s="20"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ns3:dyDescent="0.2">
       <c r="A39" s="59" t="s">
         <v>295</v>
       </c>
@@ -8428,7 +8441,7 @@
       <c r="D39" s="59"/>
       <c r="G39" s="20"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ns3:dyDescent="0.2">
       <c r="A40" s="59" t="s">
         <v>298</v>
       </c>
@@ -8441,7 +8454,7 @@
       <c r="D40" s="59"/>
       <c r="G40" s="20"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ns3:dyDescent="0.2">
       <c r="A41" s="59" t="s">
         <v>301</v>
       </c>
@@ -8454,7 +8467,7 @@
       <c r="D41" s="59"/>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ns3:dyDescent="0.2">
       <c r="A42" s="59" t="s">
         <v>304</v>
       </c>
@@ -8467,7 +8480,7 @@
       <c r="D42" s="59"/>
       <c r="G42" s="20"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ns3:dyDescent="0.2">
       <c r="A43" s="59" t="s">
         <v>307</v>
       </c>
@@ -8480,7 +8493,7 @@
       <c r="D43" s="59"/>
       <c r="G43" s="20"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ns3:dyDescent="0.2">
       <c r="A44" s="59" t="s">
         <v>310</v>
       </c>
@@ -8493,7 +8506,7 @@
       <c r="D44" s="59"/>
       <c r="G44" s="20"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ns3:dyDescent="0.2">
       <c r="A45" s="59" t="s">
         <v>313</v>
       </c>
@@ -8506,7 +8519,7 @@
       <c r="D45" s="59"/>
       <c r="G45" s="20"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ns3:dyDescent="0.2">
       <c r="A46" s="59" t="s">
         <v>316</v>
       </c>
@@ -8519,7 +8532,7 @@
       <c r="D46" s="59"/>
       <c r="G46" s="20"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ns3:dyDescent="0.2">
       <c r="A47" s="59" t="s">
         <v>319</v>
       </c>
@@ -8532,7 +8545,7 @@
       <c r="D47" s="59"/>
       <c r="G47" s="20"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ns3:dyDescent="0.2">
       <c r="A48" s="59" t="s">
         <v>322</v>
       </c>
@@ -8545,7 +8558,7 @@
       <c r="D48" s="59"/>
       <c r="G48" s="20"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ns3:dyDescent="0.2">
       <c r="A49" s="59" t="s">
         <v>325</v>
       </c>
@@ -8558,7 +8571,7 @@
       <c r="D49" s="59"/>
       <c r="G49" s="20"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ns3:dyDescent="0.2">
       <c r="A50" s="59" t="s">
         <v>328</v>
       </c>
@@ -8571,7 +8584,7 @@
       <c r="D50" s="59"/>
       <c r="G50" s="20"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ns3:dyDescent="0.2">
       <c r="A51" s="59" t="s">
         <v>331</v>
       </c>
@@ -8584,7 +8597,7 @@
       <c r="D51" s="59"/>
       <c r="G51" s="20"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ns3:dyDescent="0.2">
       <c r="A52" s="59" t="s">
         <v>334</v>
       </c>
@@ -8597,7 +8610,7 @@
       <c r="D52" s="59"/>
       <c r="G52" s="20"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ns3:dyDescent="0.2">
       <c r="A53" s="59" t="s">
         <v>337</v>
       </c>
@@ -8610,7 +8623,7 @@
       <c r="D53" s="59"/>
       <c r="G53" s="20"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ns3:dyDescent="0.2">
       <c r="A54" s="59" t="s">
         <v>340</v>
       </c>
@@ -8623,7 +8636,7 @@
       <c r="D54" s="59"/>
       <c r="G54" s="20"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ns3:dyDescent="0.2">
       <c r="A55" s="59" t="s">
         <v>343</v>
       </c>
@@ -8635,7 +8648,7 @@
       </c>
       <c r="D55" s="59"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ns3:dyDescent="0.2">
       <c r="A56" s="59" t="s">
         <v>346</v>
       </c>
@@ -8647,7 +8660,7 @@
       </c>
       <c r="D56" s="59"/>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ns3:dyDescent="0.2">
       <c r="A57" s="59" t="s">
         <v>349</v>
       </c>
@@ -8659,7 +8672,7 @@
       </c>
       <c r="D57" s="59"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ns3:dyDescent="0.2">
       <c r="A58" s="59" t="s">
         <v>352</v>
       </c>
@@ -8671,7 +8684,7 @@
       </c>
       <c r="D58" s="59"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ns3:dyDescent="0.2">
       <c r="A59" s="59" t="s">
         <v>355</v>
       </c>
@@ -8683,7 +8696,7 @@
       </c>
       <c r="D59" s="59"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ns3:dyDescent="0.2">
       <c r="A60" s="59" t="s">
         <v>358</v>
       </c>
@@ -8695,7 +8708,7 @@
       </c>
       <c r="D60" s="59"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ns3:dyDescent="0.2">
       <c r="A61" s="59" t="s">
         <v>361</v>
       </c>
@@ -8707,21 +8720,23 @@
       </c>
       <c r="D61" s="59"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ns3:dyDescent="0.2">
       <c r="A62" s="59"/>
       <c r="B62" s="60"/>
       <c r="C62" s="60"/>
       <c r="D62" s="59"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="59"/>
+    <row r="63" spans="1:7" ns3:dyDescent="0.2">
+      <c r="A63" s="59" t="s">
+        <v>404</v>
+      </c>
       <c r="B63" s="60" t="s">
         <v>364</v>
       </c>
       <c r="C63" s="60"/>
       <c r="D63" s="59"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ns3:dyDescent="0.2">
       <c r="A64" s="59" t="s">
         <v>365</v>
       </c>
@@ -8733,7 +8748,7 @@
       </c>
       <c r="D64" s="59"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ns3:dyDescent="0.2">
       <c r="A65" s="59" t="s">
         <v>368</v>
       </c>
@@ -8745,7 +8760,7 @@
       </c>
       <c r="D65" s="59"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ns3:dyDescent="0.2">
       <c r="A66" s="59" t="s">
         <v>371</v>
       </c>
@@ -8757,7 +8772,7 @@
       </c>
       <c r="D66" s="59"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ns3:dyDescent="0.2">
       <c r="A67" s="59" t="s">
         <v>374</v>
       </c>
@@ -8769,7 +8784,7 @@
       </c>
       <c r="D67" s="59"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ns3:dyDescent="0.2">
       <c r="A68" s="59" t="s">
         <v>377</v>
       </c>
@@ -8781,7 +8796,7 @@
       </c>
       <c r="D68" s="59"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ns3:dyDescent="0.2">
       <c r="A69" s="59" t="s">
         <v>380</v>
       </c>
@@ -8793,7 +8808,7 @@
       </c>
       <c r="D69" s="59"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ns3:dyDescent="0.2">
       <c r="A70" s="59" t="s">
         <v>383</v>
       </c>
@@ -8805,7 +8820,7 @@
       </c>
       <c r="D70" s="59"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ns3:dyDescent="0.2">
       <c r="A71" s="59" t="s">
         <v>386</v>
       </c>
@@ -8817,7 +8832,7 @@
       </c>
       <c r="D71" s="59"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ns3:dyDescent="0.2">
       <c r="A72" s="59" t="s">
         <v>389</v>
       </c>
@@ -8829,7 +8844,7 @@
       </c>
       <c r="D72" s="59"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ns3:dyDescent="0.2">
       <c r="A73" s="59" t="s">
         <v>392</v>
       </c>
@@ -8841,7 +8856,7 @@
       </c>
       <c r="D73" s="59"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ns3:dyDescent="0.2">
       <c r="A74" s="59" t="s">
         <v>395</v>
       </c>
@@ -8853,7 +8868,7 @@
       </c>
       <c r="D74" s="59"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ns3:dyDescent="0.2">
       <c r="A75" s="59" t="s">
         <v>398</v>
       </c>
@@ -8867,7 +8882,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:4" ns3:dyDescent="0.15">
       <c r="A76" s="61"/>
       <c r="B76" s="61"/>
       <c r="C76" s="62"/>
@@ -8881,15 +8896,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{ACD342F2-949F-8E4F-8019-9523BB9FDCE8}">
-          <x14:formula1>
-            <xm:f>Lookups!$A$3:$A$16</xm:f>
-          </x14:formula1>
-          <xm:sqref>I4:I32</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
+    <ext uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <ns5:dataValidations count="1">
+        <ns5:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" ns2:uid="{ACD342F2-949F-8E4F-8019-9523BB9FDCE8}">
+          <ns5:formula1>
+            <ns6:f>Lookups!$A$3:$A$16</ns6:f>
+          </ns5:formula1>
+          <ns6:sqref>I4:I32</ns6:sqref>
+        </ns5:dataValidation>
+      </ns5:dataValidations>
     </ext>
   </extLst>
 </worksheet>
